--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty SDL Dec 2028 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty SDL Dec 2028 Index Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5565AB-4229-410A-B7A8-BA53A4404CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DECE67-2712-49D0-92B8-72BDBF88512E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="90">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Nifty SDL Dec 2028 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -136,6 +136,9 @@
     <t>IN1920180081</t>
   </si>
   <si>
+    <t>IN2220200256</t>
+  </si>
+  <si>
     <t>IN1920180115</t>
   </si>
   <si>
@@ -148,15 +151,15 @@
     <t>IN1520180218</t>
   </si>
   <si>
+    <t>IN3320180067</t>
+  </si>
+  <si>
+    <t>IN3120180168</t>
+  </si>
+  <si>
     <t>IN1520180184</t>
   </si>
   <si>
-    <t>IN3120180168</t>
-  </si>
-  <si>
-    <t>IN2220180045</t>
-  </si>
-  <si>
     <t>IN2920180279</t>
   </si>
   <si>
@@ -166,9 +169,6 @@
     <t>IN1020220589</t>
   </si>
   <si>
-    <t>IN2220200256</t>
-  </si>
-  <si>
     <t>IN1520180176</t>
   </si>
   <si>
@@ -271,10 +271,16 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
+  </si>
+  <si>
+    <t>Debt Index Replication Factor (DIRF) as on 31-5-2025</t>
+  </si>
+  <si>
+    <t>As per SEBI circular no. SEBI/HO/IMD/PoD/P/CIR/2024/183 dated December 31,2024, with respect to introduction of mutual Funds Lite (MF Lite) framework for passively managed schemes of Mutual Funds, Debt Index Replication Factor (DIRF) is disclosed for debt oriented passive schemes.</t>
   </si>
   <si>
     <t>Scheme Riskometer</t>
@@ -299,7 +305,7 @@
     <numFmt numFmtId="165" formatCode="##0.00%"/>
     <numFmt numFmtId="166" formatCode="##0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -307,13 +313,21 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <name val="Verdana"/>
+      <sz val="8.25"/>
+      <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.25"/>
-      <name val="Microsoft Sans Serif"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
@@ -478,83 +492,93 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
@@ -583,13 +607,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -613,7 +637,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="17030700"/>
+          <a:off x="666750" y="17592675"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -630,13 +654,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -660,7 +684,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="19888200"/>
+          <a:off x="666750" y="20450175"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -996,19 +1020,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="25" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="53.5703125" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="19.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="38.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.7109375" style="25" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="27" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="53.5703125" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="19.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="38.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.7109375" style="27" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1051,1733 +1075,1733 @@
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="12">
-        <v>94949.11000000003</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0.9653058018449</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="C5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="14">
+        <v>95502.320000000022</v>
+      </c>
+      <c r="H5" s="15">
+        <v>0.95269346617799999</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="14" t="s">
+      <c r="B6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="12">
-        <v>94949.11000000003</v>
-      </c>
-      <c r="H7" s="13">
-        <v>0.9653058018449</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="C7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="14">
+        <v>95502.320000000022</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0.95269346617799999</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="14" t="s">
+      <c r="B8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="12">
-        <v>94949.11000000003</v>
-      </c>
-      <c r="H9" s="13">
-        <v>0.9653058018449</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="C9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="14">
+        <v>95502.320000000022</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.95269346617799999</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="19">
         <v>8.18</v>
       </c>
-      <c r="E10" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="18">
+      <c r="E10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="20">
         <v>17607000</v>
       </c>
-      <c r="G10" s="19">
-        <v>18337.759999999998</v>
-      </c>
-      <c r="H10" s="20">
-        <v>0.18643193307299999</v>
-      </c>
-      <c r="I10" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J10" s="14" t="s">
+      <c r="G10" s="21">
+        <v>18779.52</v>
+      </c>
+      <c r="H10" s="22">
+        <v>0.18733708251260001</v>
+      </c>
+      <c r="I10" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J10" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="19">
         <v>8.08</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="18">
-        <v>16885000</v>
-      </c>
-      <c r="G11" s="19">
-        <v>17538.09</v>
-      </c>
-      <c r="H11" s="20">
-        <v>0.17830204022240001</v>
-      </c>
-      <c r="I11" s="19">
-        <v>7.05</v>
-      </c>
-      <c r="J11" s="14" t="s">
+      <c r="E11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="20">
+        <v>14385000</v>
+      </c>
+      <c r="G11" s="21">
+        <v>15306.6</v>
+      </c>
+      <c r="H11" s="22">
+        <v>0.1526926027496</v>
+      </c>
+      <c r="I11" s="21">
+        <v>6.15</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <v>8.620000000000001</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="18">
+      <c r="E12" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="20">
         <v>9000000</v>
       </c>
-      <c r="G12" s="19">
-        <v>9465.2800000000007</v>
-      </c>
-      <c r="H12" s="20">
-        <v>9.6229334852100001E-2</v>
-      </c>
-      <c r="I12" s="19">
-        <v>7.09</v>
-      </c>
-      <c r="J12" s="14" t="s">
+      <c r="G12" s="21">
+        <v>9654.69</v>
+      </c>
+      <c r="H12" s="22">
+        <v>9.6311378414500007E-2</v>
+      </c>
+      <c r="I12" s="21">
+        <v>6.21</v>
+      </c>
+      <c r="J12" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <v>8.3800000000000008</v>
       </c>
-      <c r="E13" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="18">
+      <c r="E13" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="20">
         <v>5460000</v>
       </c>
-      <c r="G13" s="19">
-        <v>5717.94</v>
-      </c>
-      <c r="H13" s="20">
-        <v>5.8131778766600001E-2</v>
-      </c>
-      <c r="I13" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J13" s="14" t="s">
+      <c r="G13" s="21">
+        <v>5850.27</v>
+      </c>
+      <c r="H13" s="22">
+        <v>5.8359985436800002E-2</v>
+      </c>
+      <c r="I13" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J13" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="19">
         <v>8.73</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="18">
+      <c r="E14" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="20">
         <v>5000000</v>
       </c>
-      <c r="G14" s="19">
-        <v>5283.97</v>
-      </c>
-      <c r="H14" s="20">
-        <v>5.3719796823600001E-2</v>
-      </c>
-      <c r="I14" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J14" s="14" t="s">
+      <c r="G14" s="21">
+        <v>5393.12</v>
+      </c>
+      <c r="H14" s="22">
+        <v>5.37996373943E-2</v>
+      </c>
+      <c r="I14" s="21">
+        <v>6.19</v>
+      </c>
+      <c r="J14" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="19">
         <v>8.17</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="18">
+      <c r="E15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="20">
         <v>3500000</v>
       </c>
-      <c r="G15" s="19">
-        <v>3644.39</v>
-      </c>
-      <c r="H15" s="20">
-        <v>3.7050908757199998E-2</v>
-      </c>
-      <c r="I15" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J15" s="14" t="s">
+      <c r="G15" s="21">
+        <v>3731.98</v>
+      </c>
+      <c r="H15" s="22">
+        <v>3.7228760117100003E-2</v>
+      </c>
+      <c r="I15" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J15" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <v>8.84</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="18">
+      <c r="E16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="20">
         <v>3100000</v>
       </c>
-      <c r="G16" s="19">
-        <v>3282.64</v>
-      </c>
-      <c r="H16" s="20">
-        <v>3.3373155760699998E-2</v>
-      </c>
-      <c r="I16" s="19">
-        <v>7.08</v>
-      </c>
-      <c r="J16" s="14" t="s">
+      <c r="G16" s="21">
+        <v>3349.57</v>
+      </c>
+      <c r="H16" s="22">
+        <v>3.3413988827800001E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J16" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="19">
         <v>8.36</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="18">
+      <c r="E17" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="20">
         <v>3000000</v>
       </c>
-      <c r="G17" s="19">
-        <v>3141.95</v>
-      </c>
-      <c r="H17" s="20">
-        <v>3.1942822466799997E-2</v>
-      </c>
-      <c r="I17" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J17" s="14" t="s">
+      <c r="G17" s="21">
+        <v>3215.79</v>
+      </c>
+      <c r="H17" s="22">
+        <v>3.2079452327500001E-2</v>
+      </c>
+      <c r="I17" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J17" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="19">
         <v>8.6300000000000008</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="18">
+      <c r="E18" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="20">
         <v>2960000</v>
       </c>
-      <c r="G18" s="19">
-        <v>3113.96</v>
-      </c>
-      <c r="H18" s="20">
-        <v>3.1658260458799999E-2</v>
-      </c>
-      <c r="I18" s="19">
-        <v>7.08</v>
-      </c>
-      <c r="J18" s="14" t="s">
+      <c r="G18" s="21">
+        <v>3178.55</v>
+      </c>
+      <c r="H18" s="22">
+        <v>3.1707960779600003E-2</v>
+      </c>
+      <c r="I18" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J18" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="19">
         <v>8.7000000000000011</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="18">
+      <c r="E19" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="20">
         <v>2500000</v>
       </c>
-      <c r="G19" s="19">
-        <v>2639.14</v>
-      </c>
-      <c r="H19" s="20">
-        <v>2.6830974549199998E-2</v>
-      </c>
-      <c r="I19" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J19" s="14" t="s">
+      <c r="G19" s="21">
+        <v>2693.98</v>
+      </c>
+      <c r="H19" s="22">
+        <v>2.6874081635000002E-2</v>
+      </c>
+      <c r="I19" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J19" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="19">
         <v>8.08</v>
       </c>
-      <c r="E20" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="18">
+      <c r="E20" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="20">
         <v>2359800</v>
       </c>
-      <c r="G20" s="19">
-        <v>2451.2800000000002</v>
-      </c>
-      <c r="H20" s="20">
-        <v>2.4921084630999998E-2</v>
-      </c>
-      <c r="I20" s="19">
-        <v>7.05</v>
-      </c>
-      <c r="J20" s="14" t="s">
+      <c r="G20" s="21">
+        <v>2510.9899999999998</v>
+      </c>
+      <c r="H20" s="22">
+        <v>2.5048645589299999E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <v>6.15</v>
+      </c>
+      <c r="J20" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="19">
         <v>8.08</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="18">
+      <c r="E21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="20">
         <v>2186400</v>
       </c>
-      <c r="G21" s="19">
-        <v>2271.37</v>
-      </c>
-      <c r="H21" s="20">
-        <v>2.30920188629E-2</v>
-      </c>
-      <c r="I21" s="19">
-        <v>7.04</v>
-      </c>
-      <c r="J21" s="14" t="s">
+      <c r="G21" s="21">
+        <v>2326.48</v>
+      </c>
+      <c r="H21" s="22">
+        <v>2.3208046623300001E-2</v>
+      </c>
+      <c r="I21" s="21">
+        <v>6.15</v>
+      </c>
+      <c r="J21" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="19">
         <v>8.52</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="18">
+      <c r="E22" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="20">
         <v>2000000</v>
       </c>
-      <c r="G22" s="19">
-        <v>2103.7399999999998</v>
-      </c>
-      <c r="H22" s="20">
-        <v>2.13877984488E-2</v>
-      </c>
-      <c r="I22" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J22" s="14" t="s">
+      <c r="G22" s="21">
+        <v>2152.42</v>
+      </c>
+      <c r="H22" s="22">
+        <v>2.14716927345E-2</v>
+      </c>
+      <c r="I22" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J22" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="19">
+        <v>6.55</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="20">
+        <v>2000000</v>
+      </c>
+      <c r="G23" s="21">
+        <v>2030.8</v>
+      </c>
+      <c r="H23" s="22">
+        <v>2.0258459596700001E-2</v>
+      </c>
+      <c r="I23" s="21">
+        <v>6.13</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="17">
+      <c r="C24" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="19">
         <v>8.08</v>
       </c>
-      <c r="E23" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="18">
+      <c r="E24" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="20">
         <v>1528800</v>
       </c>
-      <c r="G23" s="19">
-        <v>1587.41</v>
-      </c>
-      <c r="H23" s="20">
-        <v>1.6138498643200001E-2</v>
-      </c>
-      <c r="I23" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="15" t="s">
+      <c r="G24" s="21">
+        <v>1626.75</v>
+      </c>
+      <c r="H24" s="22">
+        <v>1.6227816204899999E-2</v>
+      </c>
+      <c r="I24" s="21">
+        <v>6.15</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="17">
+      <c r="C25" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="19">
         <v>8.6</v>
       </c>
-      <c r="E24" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="18">
+      <c r="E25" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="20">
         <v>1500000</v>
       </c>
-      <c r="G24" s="19">
-        <v>1579.78</v>
-      </c>
-      <c r="H24" s="20">
-        <v>1.6060927792099999E-2</v>
-      </c>
-      <c r="I24" s="19">
-        <v>7.08</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="15" t="s">
+      <c r="G25" s="21">
+        <v>1614.88</v>
+      </c>
+      <c r="H25" s="22">
+        <v>1.6109405767900001E-2</v>
+      </c>
+      <c r="I25" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="C26" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="19">
         <v>8.19</v>
       </c>
-      <c r="E25" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="18">
+      <c r="E26" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="20">
         <v>1500000</v>
       </c>
-      <c r="G25" s="19">
-        <v>1561.98</v>
-      </c>
-      <c r="H25" s="20">
-        <v>1.5879963028199998E-2</v>
-      </c>
-      <c r="I25" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="15" t="s">
+      <c r="G26" s="21">
+        <v>1598.59</v>
+      </c>
+      <c r="H26" s="22">
+        <v>1.5946903154800001E-2</v>
+      </c>
+      <c r="I26" s="21">
+        <v>6.19</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="17">
+      <c r="C27" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="19">
         <v>8.32</v>
       </c>
-      <c r="E26" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" s="18">
+      <c r="E27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="20">
         <v>1300000</v>
       </c>
-      <c r="G26" s="19">
-        <v>1359.89</v>
-      </c>
-      <c r="H26" s="20">
-        <v>1.3825402964499999E-2</v>
-      </c>
-      <c r="I26" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="15" t="s">
+      <c r="G27" s="21">
+        <v>1391.88</v>
+      </c>
+      <c r="H27" s="22">
+        <v>1.38848457472E-2</v>
+      </c>
+      <c r="I27" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="19">
+        <v>8.73</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="20">
+        <v>1000000</v>
+      </c>
+      <c r="G28" s="21">
+        <v>1079.47</v>
+      </c>
+      <c r="H28" s="22">
+        <v>1.07683668411E-2</v>
+      </c>
+      <c r="I28" s="21">
+        <v>6.19</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="19">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="20">
+        <v>1000000</v>
+      </c>
+      <c r="G29" s="21">
+        <v>1076.52</v>
+      </c>
+      <c r="H29" s="22">
+        <v>1.0738938804900001E-2</v>
+      </c>
+      <c r="I29" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="17">
+      <c r="C30" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="19">
         <v>8.57</v>
       </c>
-      <c r="E27" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="18">
+      <c r="E30" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="20">
         <v>1000000</v>
       </c>
-      <c r="G27" s="19">
-        <v>1053.1400000000001</v>
-      </c>
-      <c r="H27" s="20">
-        <v>1.07068107553E-2</v>
-      </c>
-      <c r="I27" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="G30" s="21">
+        <v>1076.47</v>
+      </c>
+      <c r="H30" s="22">
+        <v>1.0738440024599999E-2</v>
+      </c>
+      <c r="I30" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="19">
+        <v>8.09</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="20">
+        <v>1000000</v>
+      </c>
+      <c r="G31" s="21">
+        <v>1063.56</v>
+      </c>
+      <c r="H31" s="22">
+        <v>1.0609654958E-2</v>
+      </c>
+      <c r="I31" s="21">
+        <v>6.17</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="20">
+        <v>1000000</v>
+      </c>
+      <c r="G32" s="21">
+        <v>1043.96</v>
+      </c>
+      <c r="H32" s="22">
+        <v>1.04141330907E-2</v>
+      </c>
+      <c r="I32" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="19">
+        <v>8.58</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="20">
+        <v>500000</v>
+      </c>
+      <c r="G33" s="21">
+        <v>538.21</v>
+      </c>
+      <c r="H33" s="22">
+        <v>5.3689706221999997E-3</v>
+      </c>
+      <c r="I33" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="19">
         <v>8.5299999999999994</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="G28" s="19">
-        <v>1052.5</v>
-      </c>
-      <c r="H28" s="20">
-        <v>1.0700304157000001E-2</v>
-      </c>
-      <c r="I28" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="15" t="s">
+      <c r="E34" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="20">
+        <v>500000</v>
+      </c>
+      <c r="G34" s="21">
+        <v>538.03</v>
+      </c>
+      <c r="H34" s="22">
+        <v>5.3671750132000002E-3</v>
+      </c>
+      <c r="I34" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="19">
+        <v>8.43</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="20">
+        <v>500000</v>
+      </c>
+      <c r="G35" s="21">
+        <v>536.54999999999995</v>
+      </c>
+      <c r="H35" s="22">
+        <v>5.3524111171000003E-3</v>
+      </c>
+      <c r="I35" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J35" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="19">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="20">
+        <v>500000</v>
+      </c>
+      <c r="G36" s="21">
+        <v>535.34</v>
+      </c>
+      <c r="H36" s="22">
+        <v>5.3403406344000003E-3</v>
+      </c>
+      <c r="I36" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="19">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="20">
+        <v>500000</v>
+      </c>
+      <c r="G37" s="21">
+        <v>534.64</v>
+      </c>
+      <c r="H37" s="22">
+        <v>5.3333577106000002E-3</v>
+      </c>
+      <c r="I37" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="17">
-        <v>8.42</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="G29" s="19">
-        <v>1045.5</v>
-      </c>
-      <c r="H29" s="20">
-        <v>1.0629138238600001E-2</v>
-      </c>
-      <c r="I29" s="19">
-        <v>7.05</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="15" t="s">
+      <c r="C38" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="19">
+        <v>6.7</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="20">
+        <v>500000</v>
+      </c>
+      <c r="G38" s="21">
+        <v>509.79</v>
+      </c>
+      <c r="H38" s="22">
+        <v>5.0854639146E-3</v>
+      </c>
+      <c r="I38" s="21">
+        <v>6.13</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="19">
+        <v>8.6</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="20">
+        <v>200000</v>
+      </c>
+      <c r="G39" s="21">
+        <v>215.25</v>
+      </c>
+      <c r="H39" s="22">
+        <v>2.1472490781999998E-3</v>
+      </c>
+      <c r="I39" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="17">
-        <v>8.09</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="G30" s="19">
-        <v>1038.1600000000001</v>
-      </c>
-      <c r="H30" s="20">
-        <v>1.05545156899E-2</v>
-      </c>
-      <c r="I30" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="17">
-        <v>7.5</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="G31" s="19">
-        <v>1017.45</v>
-      </c>
-      <c r="H31" s="20">
-        <v>1.0343966237100001E-2</v>
-      </c>
-      <c r="I31" s="19">
-        <v>7.09</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="17">
-        <v>6.55</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="G32" s="19">
-        <v>988.49</v>
-      </c>
-      <c r="H32" s="20">
-        <v>1.00495426662E-2</v>
-      </c>
-      <c r="I32" s="19">
-        <v>7.02</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="15" t="s">
+      <c r="C40" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="19">
+        <v>8.76</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="20">
+        <v>100000</v>
+      </c>
+      <c r="G40" s="21">
+        <v>107.9</v>
+      </c>
+      <c r="H40" s="22">
+        <v>1.0763678306E-3</v>
+      </c>
+      <c r="I40" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="19">
+        <v>8.5400000000000009</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="20">
+        <v>100000</v>
+      </c>
+      <c r="G41" s="21">
+        <v>107.61</v>
+      </c>
+      <c r="H41" s="22">
+        <v>1.0734749049999999E-3</v>
+      </c>
+      <c r="I41" s="21">
+        <v>6.18</v>
+      </c>
+      <c r="J41" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="19">
+        <v>8.6</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="20">
+        <v>50000</v>
+      </c>
+      <c r="G42" s="21">
+        <v>53.84</v>
+      </c>
+      <c r="H42" s="22">
+        <v>5.3708659870000005E-4</v>
+      </c>
+      <c r="I42" s="21">
+        <v>6.19</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="19">
+        <v>8.370000000000001</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="20">
+        <v>50000</v>
+      </c>
+      <c r="G43" s="21">
+        <v>53.58</v>
+      </c>
+      <c r="H43" s="22">
+        <v>5.3449294129999999E-4</v>
+      </c>
+      <c r="I43" s="21">
+        <v>6.17</v>
+      </c>
+      <c r="J43" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="17">
-        <v>8.58</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="18">
-        <v>500000</v>
-      </c>
-      <c r="G33" s="19">
-        <v>526.63</v>
-      </c>
-      <c r="H33" s="20">
-        <v>5.3540153711999997E-3</v>
-      </c>
-      <c r="I33" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="17">
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="18">
-        <v>500000</v>
-      </c>
-      <c r="G34" s="19">
-        <v>526.15</v>
-      </c>
-      <c r="H34" s="20">
-        <v>5.3491354224999999E-3</v>
-      </c>
-      <c r="I34" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="17">
-        <v>8.43</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="18">
-        <v>500000</v>
-      </c>
-      <c r="G35" s="19">
-        <v>524.55999999999995</v>
-      </c>
-      <c r="H35" s="20">
-        <v>5.3329705924999998E-3</v>
-      </c>
-      <c r="I35" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="17">
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" s="18">
-        <v>500000</v>
-      </c>
-      <c r="G36" s="19">
-        <v>524.38</v>
-      </c>
-      <c r="H36" s="20">
-        <v>5.3311406117000004E-3</v>
-      </c>
-      <c r="I36" s="19">
-        <v>7.08</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="17">
-        <v>8.4700000000000006</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="18">
-        <v>500000</v>
-      </c>
-      <c r="G37" s="19">
-        <v>523.99</v>
-      </c>
-      <c r="H37" s="20">
-        <v>5.3271756533999999E-3</v>
-      </c>
-      <c r="I37" s="19">
-        <v>7.04</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="17">
-        <v>6.7</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="18">
-        <v>500000</v>
-      </c>
-      <c r="G38" s="19">
-        <v>496.71</v>
-      </c>
-      <c r="H38" s="20">
-        <v>5.0498319028999998E-3</v>
-      </c>
-      <c r="I38" s="19">
-        <v>7.02</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="17">
-        <v>8.6</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" s="18">
-        <v>200000</v>
-      </c>
-      <c r="G39" s="19">
-        <v>210.69</v>
-      </c>
-      <c r="H39" s="20">
-        <v>2.1419924776999999E-3</v>
-      </c>
-      <c r="I39" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="17">
-        <v>8.76</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" s="18">
-        <v>100000</v>
-      </c>
-      <c r="G40" s="19">
-        <v>105.69</v>
-      </c>
-      <c r="H40" s="20">
-        <v>1.0745037020000001E-3</v>
-      </c>
-      <c r="I40" s="19">
-        <v>7.08</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" s="17">
-        <v>8.5400000000000009</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" s="18">
-        <v>100000</v>
-      </c>
-      <c r="G41" s="19">
-        <v>105.23</v>
-      </c>
-      <c r="H41" s="20">
-        <v>1.0698270845000001E-3</v>
-      </c>
-      <c r="I41" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="17">
-        <v>8.6</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" s="18">
-        <v>50000</v>
-      </c>
-      <c r="G42" s="19">
-        <v>52.69</v>
-      </c>
-      <c r="H42" s="20">
-        <v>5.3567603420000005E-4</v>
-      </c>
-      <c r="I42" s="19">
-        <v>7.07</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="17">
-        <v>8.370000000000001</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="18">
-        <v>50000</v>
-      </c>
-      <c r="G43" s="19">
-        <v>52.39</v>
-      </c>
-      <c r="H43" s="20">
-        <v>5.3262606630000001E-4</v>
-      </c>
-      <c r="I43" s="19">
-        <v>7.05</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="19">
         <v>8.5</v>
       </c>
-      <c r="E44" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="18">
+      <c r="E44" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="20">
         <v>23000</v>
       </c>
-      <c r="G44" s="19">
-        <v>24.19</v>
-      </c>
-      <c r="H44" s="20">
-        <v>2.4592908079999997E-4</v>
-      </c>
-      <c r="I44" s="19">
-        <v>7.06</v>
-      </c>
-      <c r="J44" s="14" t="s">
+      <c r="G44" s="21">
+        <v>24.74</v>
+      </c>
+      <c r="H44" s="22">
+        <v>2.4679647939999998E-4</v>
+      </c>
+      <c r="I44" s="21">
+        <v>6.16</v>
+      </c>
+      <c r="J44" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="14" t="s">
+      <c r="B45" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="12" t="s">
+      <c r="C46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H46" s="13" t="s">
+      <c r="H46" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I46" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="14" t="s">
+      <c r="I46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="14" t="s">
+      <c r="B47" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="12" t="s">
+      <c r="C48" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H48" s="13" t="s">
+      <c r="H48" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="14" t="s">
+      <c r="I48" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="14" t="s">
+      <c r="B49" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="12" t="s">
+      <c r="C50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="14" t="s">
+      <c r="I50" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="14" t="s">
+      <c r="B51" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="12" t="s">
+      <c r="C52" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="14" t="s">
+      <c r="I52" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="14" t="s">
+      <c r="B53" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="12" t="s">
+      <c r="C54" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I54" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="14" t="s">
+      <c r="I54" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="14" t="s">
+      <c r="B55" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="12" t="s">
+      <c r="C56" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="14" t="s">
+      <c r="I56" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="14" t="s">
+      <c r="B57" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C58" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="12" t="s">
+      <c r="C58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H58" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I58" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="14" t="s">
+      <c r="I58" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="14" t="s">
+      <c r="B59" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="12" t="s">
+      <c r="C60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H60" s="13" t="s">
+      <c r="H60" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="14" t="s">
+      <c r="I60" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="14" t="s">
+      <c r="B61" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="12" t="s">
+      <c r="C62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H62" s="13" t="s">
+      <c r="H62" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="14" t="s">
+      <c r="I62" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="14" t="s">
+      <c r="B63" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C64" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="12" t="s">
+      <c r="C64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="14" t="s">
+      <c r="I64" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="14" t="s">
+      <c r="B65" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="12" t="s">
+      <c r="C66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H66" s="13" t="s">
+      <c r="H66" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="14" t="s">
+      <c r="I66" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="14" t="s">
+      <c r="B67" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="12" t="s">
+      <c r="C68" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I68" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="14" t="s">
+      <c r="I68" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="14" t="s">
+      <c r="B69" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="12" t="s">
+      <c r="C70" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H70" s="13" t="s">
+      <c r="H70" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I70" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="14" t="s">
+      <c r="I70" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="14" t="s">
+      <c r="B71" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="12">
-        <v>1907.35</v>
-      </c>
-      <c r="H72" s="13">
-        <v>1.9391187775700001E-2</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="14" t="s">
+      <c r="C72" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="14">
+        <v>2269.02</v>
+      </c>
+      <c r="H72" s="15">
+        <v>2.2634848332799998E-2</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="14" t="s">
+      <c r="B73" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C74" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="22">
-        <v>1505.2299622799619</v>
-      </c>
-      <c r="H74" s="23">
-        <v>1.5303010377893989E-2</v>
-      </c>
-      <c r="I74" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="24" t="s">
+      <c r="C74" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="24">
+        <v>2473.2018072999781</v>
+      </c>
+      <c r="H74" s="25">
+        <v>2.4671685487417477E-2</v>
+      </c>
+      <c r="I74" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="26" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="22">
-        <v>98361.689962279997</v>
-      </c>
-      <c r="H75" s="23">
-        <v>0.99999999999849398</v>
-      </c>
-      <c r="I75" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="24" t="s">
+      <c r="C75" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="24">
+        <v>100244.5418073</v>
+      </c>
+      <c r="H75" s="25">
+        <v>0.99999999999821754</v>
+      </c>
+      <c r="I75" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="26" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2837,23 +2861,46 @@
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
     </row>
-    <row r="85" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B85" s="25" t="s">
+    <row r="83" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="100" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B100" s="25" t="s">
+      <c r="C83" s="29">
+        <v>0.9774525094396358</v>
+      </c>
+      <c r="D83" s="30"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+    </row>
+    <row r="84" spans="2:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="101" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B101" s="25" t="s">
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+    </row>
+    <row r="87" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B87" s="27" t="s">
         <v>87</v>
       </c>
     </row>
+    <row r="102" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B102" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B84:H84"/>
     <mergeCell ref="B80:H80"/>
     <mergeCell ref="B81:H81"/>
     <mergeCell ref="B82:H82"/>
